--- a/database/event/6138/event_6138_evp_summary.xlsx
+++ b/database/event/6138/event_6138_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.7928</v>
+        <v>10.8174</v>
       </c>
       <c r="C2" t="n">
-        <v>5.2117</v>
+        <v>5.2235</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9387</v>
+        <v>3.8657</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7928</v>
+        <v>10.8174</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2934</v>
+        <v>4.318</v>
       </c>
       <c r="G2" t="n">
         <v>6.4994</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4289</v>
+        <v>4.4676</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4495</v>
+        <v>4.5052</v>
       </c>
       <c r="J2" t="n">
         <v>6.6426</v>
@@ -529,7 +529,7 @@
         <v>236</v>
       </c>
       <c r="M2" t="n">
-        <v>11.0921</v>
+        <v>11.1478</v>
       </c>
       <c r="N2" t="n">
         <v>417</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.1616</v>
+        <v>10.7649</v>
       </c>
       <c r="C3" t="n">
-        <v>4.9069</v>
+        <v>5.1982</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6837</v>
+        <v>3.8448</v>
       </c>
       <c r="E3" t="n">
-        <v>10.1616</v>
+        <v>10.7649</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8987</v>
+        <v>4.502</v>
       </c>
       <c r="G3" t="n">
         <v>6.2629</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8987</v>
+        <v>4.7561</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9168</v>
+        <v>4.7962</v>
       </c>
       <c r="J3" t="n">
         <v>6.2629</v>
@@ -575,7 +575,7 @@
         <v>236</v>
       </c>
       <c r="M3" t="n">
-        <v>10.1797</v>
+        <v>11.0591</v>
       </c>
       <c r="N3" t="n">
         <v>417</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2053</v>
+        <v>5.7995</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5135</v>
+        <v>2.8005</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6815</v>
+        <v>1.8666</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2053</v>
+        <v>5.7995</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9581</v>
+        <v>3.5523</v>
       </c>
       <c r="G4" t="n">
         <v>2.2472</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9581</v>
+        <v>3.5523</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9719</v>
+        <v>3.5822</v>
       </c>
       <c r="J4" t="n">
         <v>2.2472</v>
@@ -621,7 +621,7 @@
         <v>236</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2191</v>
+        <v>5.8294</v>
       </c>
       <c r="N4" t="n">
         <v>417</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1342</v>
+        <v>5.4733</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4792</v>
+        <v>2.643</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6527</v>
+        <v>1.7367</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1342</v>
+        <v>5.4733</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8106</v>
+        <v>4.3612</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3235</v>
+        <v>1.1121</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8106</v>
+        <v>4.5353</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8106</v>
+        <v>4.5735</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3235</v>
+        <v>1.1121</v>
       </c>
       <c r="K5" t="n">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="L5" t="n">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1341</v>
+        <v>5.6856</v>
       </c>
       <c r="N5" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.772</v>
+        <v>5.2372</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3043</v>
+        <v>2.529</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5064</v>
+        <v>1.6426</v>
       </c>
       <c r="E6" t="n">
-        <v>4.772</v>
+        <v>5.2372</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6599</v>
+        <v>2.9136</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1121</v>
+        <v>2.3235</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6599</v>
+        <v>2.9136</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6769</v>
+        <v>2.9136</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1121</v>
+        <v>2.3235</v>
       </c>
       <c r="K6" t="n">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="L6" t="n">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="M6" t="n">
-        <v>4.789</v>
+        <v>5.2371</v>
       </c>
       <c r="N6" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +732,7 @@
         <v>2.1761</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3991</v>
+        <v>1.3514</v>
       </c>
       <c r="E7" t="n">
         <v>4.5064</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1474</v>
+        <v>4.2233</v>
       </c>
       <c r="C8" t="n">
-        <v>2.0027</v>
+        <v>2.0394</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2541</v>
+        <v>1.2387</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1474</v>
+        <v>4.2233</v>
       </c>
       <c r="F8" t="n">
-        <v>4.1749</v>
+        <v>4.139</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0275</v>
+        <v>0.0843</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2363</v>
+        <v>4.1868</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4336</v>
+        <v>4.1868</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0275</v>
+        <v>0.0843</v>
       </c>
       <c r="K8" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="L8" t="n">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4061</v>
+        <v>4.2711</v>
       </c>
       <c r="N8" t="n">
-        <v>294</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>faveN</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8186</v>
+        <v>4.1518</v>
       </c>
       <c r="C9" t="n">
-        <v>1.8439</v>
+        <v>2.0048</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1213</v>
+        <v>1.2102</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8186</v>
+        <v>4.1518</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2126</v>
+        <v>4.1793</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.394</v>
+        <v>-0.0275</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3877</v>
+        <v>4.2538</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5563</v>
+        <v>3.4478</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.394</v>
+        <v>-0.0275</v>
       </c>
       <c r="K9" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1623</v>
+        <v>3.4203</v>
       </c>
       <c r="N9" t="n">
-        <v>236</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.448</v>
+        <v>4.1187</v>
       </c>
       <c r="C10" t="n">
-        <v>1.665</v>
+        <v>1.9888</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9716</v>
+        <v>1.197</v>
       </c>
       <c r="E10" t="n">
-        <v>3.448</v>
+        <v>4.1187</v>
       </c>
       <c r="F10" t="n">
-        <v>3.448</v>
+        <v>4.1187</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.448</v>
+        <v>4.1551</v>
       </c>
       <c r="I10" t="n">
-        <v>3.448</v>
+        <v>4.1551</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.448</v>
+        <v>4.1551</v>
       </c>
       <c r="N10" t="n">
         <v>187</v>
@@ -906,277 +906,277 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>faveN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.373</v>
+        <v>3.8186</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6288</v>
+        <v>1.8439</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9413</v>
+        <v>1.0774</v>
       </c>
       <c r="E11" t="n">
-        <v>3.373</v>
+        <v>3.8186</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2887</v>
+        <v>4.2126</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0843</v>
+        <v>-0.394</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2887</v>
+        <v>4.3877</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2887</v>
+        <v>3.5563</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0843</v>
+        <v>-0.394</v>
       </c>
       <c r="K11" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="L11" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="M11" t="n">
-        <v>3.373</v>
+        <v>3.1623</v>
       </c>
       <c r="N11" t="n">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9704</v>
+        <v>3.1044</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4344</v>
+        <v>1.4991</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7786</v>
+        <v>0.7929</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9704</v>
+        <v>3.1044</v>
       </c>
       <c r="F12" t="n">
-        <v>0.733</v>
+        <v>3.8433</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2374</v>
+        <v>-0.7389</v>
       </c>
       <c r="H12" t="n">
-        <v>0.733</v>
+        <v>3.8433</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7364000000000001</v>
+        <v>3.1151</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2374</v>
+        <v>-0.7389</v>
       </c>
       <c r="K12" t="n">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="L12" t="n">
-        <v>236</v>
+        <v>129</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9738</v>
+        <v>2.3762</v>
       </c>
       <c r="N12" t="n">
-        <v>417</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9236</v>
+        <v>3.0588</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4118</v>
+        <v>1.477</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7597</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9236</v>
+        <v>3.0588</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5813</v>
+        <v>3.5603</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3423</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5813</v>
+        <v>3.5603</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5933</v>
+        <v>2.8857</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3423</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="L13" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9356</v>
+        <v>2.3842</v>
       </c>
       <c r="N13" t="n">
-        <v>293</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.796</v>
+        <v>2.9676</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3501</v>
+        <v>1.433</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>2.796</v>
+        <v>2.9676</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2975</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5014999999999999</v>
+        <v>2.2374</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2975</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6727</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5014999999999999</v>
+        <v>2.2374</v>
       </c>
       <c r="K14" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="L14" t="n">
-        <v>74</v>
+        <v>236</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1712</v>
+        <v>2.9738</v>
       </c>
       <c r="N14" t="n">
-        <v>236</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7954</v>
+        <v>2.914</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3498</v>
+        <v>1.4071</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7079</v>
+        <v>0.717</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7954</v>
+        <v>2.914</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2529</v>
+        <v>2.5717</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5425</v>
+        <v>0.3423</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2529</v>
+        <v>2.5717</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2529</v>
+        <v>2.5933</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5425</v>
+        <v>0.3423</v>
       </c>
       <c r="K15" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="L15" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7954</v>
+        <v>2.9356</v>
       </c>
       <c r="N15" t="n">
-        <v>242</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7377</v>
+        <v>2.7954</v>
       </c>
       <c r="C16" t="n">
-        <v>1.322</v>
+        <v>1.3498</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6846</v>
+        <v>0.6698</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7377</v>
+        <v>2.7954</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4766</v>
+        <v>2.2529</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7389</v>
+        <v>0.5425</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4766</v>
+        <v>2.2529</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8179</v>
+        <v>2.2529</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7389</v>
+        <v>0.5425</v>
       </c>
       <c r="K16" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="L16" t="n">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="M16" t="n">
-        <v>2.079</v>
+        <v>2.7954</v>
       </c>
       <c r="N16" t="n">
-        <v>294</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17">
@@ -1192,7 +1192,7 @@
         <v>1.3178</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6811</v>
+        <v>0.6433</v>
       </c>
       <c r="E17" t="n">
         <v>2.729</v>
@@ -1238,7 +1238,7 @@
         <v>1.2112</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5919</v>
+        <v>0.5554</v>
       </c>
       <c r="E18" t="n">
         <v>2.5082</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4869</v>
+        <v>2.4752</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2009</v>
+        <v>1.1952</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5833</v>
+        <v>0.5422</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4869</v>
+        <v>2.4752</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1393</v>
+        <v>3.1276</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6524</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1393</v>
+        <v>3.1276</v>
       </c>
       <c r="I19" t="n">
         <v>3.1539</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3705</v>
+        <v>2.385</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1447</v>
+        <v>1.1517</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5363</v>
+        <v>0.5063</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3705</v>
+        <v>2.385</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6784</v>
+        <v>2.6929</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3079</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6784</v>
+        <v>2.6929</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1709</v>
+        <v>2.1827</v>
       </c>
       <c r="J20" t="n">
         <v>-0.3079</v>
@@ -1357,7 +1357,7 @@
         <v>74</v>
       </c>
       <c r="M20" t="n">
-        <v>1.863</v>
+        <v>1.8748</v>
       </c>
       <c r="N20" t="n">
         <v>236</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.3149</v>
+        <v>2.3222</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1178</v>
+        <v>1.1213</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5138</v>
+        <v>0.4813</v>
       </c>
       <c r="E21" t="n">
-        <v>2.3149</v>
+        <v>2.3222</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3149</v>
+        <v>1.5074</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.8148</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3149</v>
+        <v>1.5074</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3149</v>
+        <v>1.2218</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.8148</v>
       </c>
       <c r="K21" t="n">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3149</v>
+        <v>2.0366</v>
       </c>
       <c r="N21" t="n">
-        <v>174</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.278</v>
+        <v>2.3149</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1</v>
+        <v>1.1178</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4989</v>
+        <v>0.4783</v>
       </c>
       <c r="E22" t="n">
-        <v>2.278</v>
+        <v>2.3149</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4632</v>
+        <v>2.3149</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8148</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4632</v>
+        <v>2.3149</v>
       </c>
       <c r="I22" t="n">
-        <v>1.186</v>
+        <v>2.3149</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8148</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="L22" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0008</v>
+        <v>2.3149</v>
       </c>
       <c r="N22" t="n">
-        <v>294</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23">
@@ -1468,7 +1468,7 @@
         <v>1.0117</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4251</v>
+        <v>0.3908</v>
       </c>
       <c r="E23" t="n">
         <v>2.0952</v>
@@ -1504,630 +1504,630 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.0156</v>
+        <v>2.074</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.0015</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3929</v>
+        <v>0.3824</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0156</v>
+        <v>2.074</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3852</v>
+        <v>2.074</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6304</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3852</v>
+        <v>2.074</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1228</v>
+        <v>2.074</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6304</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="L24" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.7532</v>
+        <v>2.074</v>
       </c>
       <c r="N24" t="n">
-        <v>294</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0043</v>
+        <v>2.0156</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9678</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3883</v>
+        <v>0.3591</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0043</v>
+        <v>2.0156</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0043</v>
+        <v>1.3852</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.6304</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0043</v>
+        <v>1.3852</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0043</v>
+        <v>1.1228</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.6304</v>
       </c>
       <c r="K25" t="n">
-        <v>187</v>
+        <v>165</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0043</v>
+        <v>1.7532</v>
       </c>
       <c r="N25" t="n">
-        <v>187</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>JOTA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.5316</v>
+        <v>2.0047</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7396</v>
+        <v>0.968</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1974</v>
+        <v>0.3548</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5316</v>
+        <v>2.0047</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5316</v>
+        <v>2.0047</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.5316</v>
+        <v>2.0047</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5316</v>
+        <v>2.0047</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5316</v>
+        <v>2.0047</v>
       </c>
       <c r="N26" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JOTA</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3745</v>
+        <v>1.8803</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6637</v>
+        <v>0.908</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1339</v>
+        <v>0.3052</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3745</v>
+        <v>1.8803</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3745</v>
+        <v>-0.0136</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.8939</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3745</v>
+        <v>-0.0136</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3745</v>
+        <v>-0.0137</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.8939</v>
       </c>
       <c r="K27" t="n">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="M27" t="n">
-        <v>1.3745</v>
+        <v>1.8802</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3394</v>
+        <v>1.563</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6468</v>
+        <v>0.7547</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1197</v>
+        <v>0.1788</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3394</v>
+        <v>1.563</v>
       </c>
       <c r="F28" t="n">
-        <v>0.776</v>
+        <v>1.7134</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5634</v>
+        <v>-0.1504</v>
       </c>
       <c r="H28" t="n">
-        <v>0.776</v>
+        <v>1.7134</v>
       </c>
       <c r="I28" t="n">
-        <v>0.776</v>
+        <v>1.7134</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5634</v>
+        <v>-0.1504</v>
       </c>
       <c r="K28" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L28" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3394</v>
+        <v>1.563</v>
       </c>
       <c r="N28" t="n">
-        <v>296</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3081</v>
+        <v>1.5316</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6317</v>
+        <v>0.7396</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1071</v>
+        <v>0.1663</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3081</v>
+        <v>1.5316</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5858</v>
+        <v>1.5316</v>
       </c>
       <c r="G29" t="n">
-        <v>1.8939</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5858</v>
+        <v>1.5316</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5885</v>
+        <v>1.5316</v>
       </c>
       <c r="J29" t="n">
-        <v>1.8939</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="L29" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3054</v>
+        <v>1.5316</v>
       </c>
       <c r="N29" t="n">
-        <v>417</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2808</v>
+        <v>1.3394</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6185</v>
+        <v>0.6468</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0961</v>
+        <v>0.0897</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2808</v>
+        <v>1.3394</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4312</v>
+        <v>0.776</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1504</v>
+        <v>0.5634</v>
       </c>
       <c r="H30" t="n">
-        <v>1.4312</v>
+        <v>0.776</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4312</v>
+        <v>0.776</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1504</v>
+        <v>0.5634</v>
       </c>
       <c r="K30" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L30" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2808</v>
+        <v>1.3394</v>
       </c>
       <c r="N30" t="n">
-        <v>242</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1685</v>
+        <v>1.2226</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5642</v>
+        <v>0.5904</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0507</v>
+        <v>0.0432</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1685</v>
+        <v>1.2226</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9103</v>
+        <v>1.2226</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2582</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9103</v>
+        <v>1.2226</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9103</v>
+        <v>1.2226</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2582</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="L31" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1685</v>
+        <v>1.2226</v>
       </c>
       <c r="N31" t="n">
-        <v>296</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1661</v>
+        <v>1.1685</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5631</v>
+        <v>0.5642</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0497</v>
+        <v>0.0216</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1661</v>
+        <v>1.1685</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1661</v>
+        <v>0.9103</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.2582</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1661</v>
+        <v>0.9103</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1661</v>
+        <v>0.9103</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.2582</v>
       </c>
       <c r="K32" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1661</v>
+        <v>1.1685</v>
       </c>
       <c r="N32" t="n">
-        <v>145</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1468</v>
+        <v>1.1661</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5538</v>
+        <v>0.5631</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0419</v>
+        <v>0.0207</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1468</v>
+        <v>1.1661</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1468</v>
+        <v>1.1661</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1468</v>
+        <v>1.1661</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1468</v>
+        <v>1.1661</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1468</v>
+        <v>1.1661</v>
       </c>
       <c r="N33" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9678</v>
+        <v>1.1468</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4673</v>
+        <v>0.5538</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0304</v>
+        <v>0.013</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9678</v>
+        <v>1.1468</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9678</v>
+        <v>1.1468</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9678</v>
+        <v>1.1468</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9678</v>
+        <v>1.1468</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9678</v>
+        <v>1.1468</v>
       </c>
       <c r="N34" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Farlig</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9389</v>
+        <v>1.0864</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4534</v>
+        <v>0.5246</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0421</v>
+        <v>-0.0111</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9389</v>
+        <v>1.0864</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9389</v>
+        <v>1.76</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.6736</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9389</v>
+        <v>1.76</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9389</v>
+        <v>1.7748</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.6736</v>
       </c>
       <c r="K35" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9389</v>
+        <v>1.1012</v>
       </c>
       <c r="N35" t="n">
-        <v>145</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>Farlig</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9191</v>
+        <v>0.9389</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4438</v>
+        <v>0.4534</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0501</v>
+        <v>-0.0699</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9191</v>
+        <v>0.9389</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9191</v>
+        <v>0.9389</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9191</v>
+        <v>0.9389</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9191</v>
+        <v>0.9389</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9191</v>
+        <v>0.9389</v>
       </c>
       <c r="N36" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8994</v>
+        <v>0.9191</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4343</v>
+        <v>0.4438</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.058</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8994</v>
+        <v>0.9191</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8994</v>
+        <v>0.9191</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8994</v>
+        <v>0.9191</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8994</v>
+        <v>0.9191</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8994</v>
+        <v>0.9191</v>
       </c>
       <c r="N37" t="n">
         <v>135</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5918</v>
+        <v>0.8994</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2858</v>
+        <v>0.4343</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1823</v>
+        <v>-0.0856</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5918</v>
+        <v>0.8994</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5918</v>
+        <v>0.8994</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5918</v>
+        <v>0.8994</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5918</v>
+        <v>0.8994</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5918</v>
+        <v>0.8994</v>
       </c>
       <c r="N38" t="n">
         <v>135</v>
@@ -2194,277 +2194,277 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>BIT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5242</v>
+        <v>0.6922</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2531</v>
+        <v>0.3343</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2096</v>
+        <v>-0.1681</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5242</v>
+        <v>0.6922</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5242</v>
+        <v>0.6922</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5242</v>
+        <v>0.6922</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5242</v>
+        <v>0.6922</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5242</v>
+        <v>0.6922</v>
       </c>
       <c r="N39" t="n">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3949</v>
+        <v>0.6029</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1907</v>
+        <v>0.2911</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2618</v>
+        <v>-0.2037</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3949</v>
+        <v>0.6029</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3949</v>
+        <v>0.6029</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3949</v>
+        <v>0.6029</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3949</v>
+        <v>0.6029</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3949</v>
+        <v>0.6029</v>
       </c>
       <c r="N40" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3679</v>
+        <v>0.5242</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1777</v>
+        <v>0.2531</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2727</v>
+        <v>-0.2351</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3679</v>
+        <v>0.5242</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0415</v>
+        <v>0.5242</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6736</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0415</v>
+        <v>0.5242</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0463</v>
+        <v>0.5242</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6736</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="L41" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3727</v>
+        <v>0.5242</v>
       </c>
       <c r="N41" t="n">
-        <v>293</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Tuurtle</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3273</v>
+        <v>0.4093</v>
       </c>
       <c r="C42" t="n">
-        <v>0.158</v>
+        <v>0.1976</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2891</v>
+        <v>-0.2808</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3273</v>
+        <v>0.4093</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3273</v>
+        <v>0.4093</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3273</v>
+        <v>0.4093</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3273</v>
+        <v>0.4093</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3273</v>
+        <v>0.4093</v>
       </c>
       <c r="N42" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BIT</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3268</v>
+        <v>0.3949</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1578</v>
+        <v>0.1907</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2893</v>
+        <v>-0.2866</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3268</v>
+        <v>0.3949</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3268</v>
+        <v>0.3949</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3268</v>
+        <v>0.3949</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3268</v>
+        <v>0.3949</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3268</v>
+        <v>0.3949</v>
       </c>
       <c r="N43" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tuurtle</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3171</v>
+        <v>0.3273</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1531</v>
+        <v>0.158</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2933</v>
+        <v>-0.3135</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3171</v>
+        <v>0.3273</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3171</v>
+        <v>0.3273</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3171</v>
+        <v>0.3273</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3171</v>
+        <v>0.3273</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3171</v>
+        <v>0.3273</v>
       </c>
       <c r="N44" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45">
@@ -2480,7 +2480,7 @@
         <v>0.1377</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3061</v>
+        <v>-0.3303</v>
       </c>
       <c r="E45" t="n">
         <v>0.2852</v>
@@ -2526,7 +2526,7 @@
         <v>0.1061</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3326</v>
+        <v>-0.3563</v>
       </c>
       <c r="E46" t="n">
         <v>0.2198</v>
@@ -2572,7 +2572,7 @@
         <v>0.0309</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3955</v>
+        <v>-0.4185</v>
       </c>
       <c r="E47" t="n">
         <v>0.0639</v>
@@ -2618,7 +2618,7 @@
         <v>-0.0441</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4583</v>
+        <v>-0.4803</v>
       </c>
       <c r="E48" t="n">
         <v>-0.0914</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0895</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4962</v>
+        <v>-0.5177</v>
       </c>
       <c r="E49" t="n">
         <v>-0.1853</v>
@@ -2710,7 +2710,7 @@
         <v>-0.1157</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5182</v>
+        <v>-0.5394</v>
       </c>
       <c r="E50" t="n">
         <v>-0.2397</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1167</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.519</v>
+        <v>-0.5402</v>
       </c>
       <c r="E51" t="n">
         <v>-0.2417</v>
@@ -2802,7 +2802,7 @@
         <v>-0.139</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5376</v>
+        <v>-0.5586</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2878</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1422</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5403</v>
+        <v>-0.5612</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2944</v>
@@ -2894,7 +2894,7 @@
         <v>-0.182</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5737</v>
+        <v>-0.5941</v>
       </c>
       <c r="E54" t="n">
         <v>-0.377</v>
@@ -2940,7 +2940,7 @@
         <v>-0.211</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5979</v>
+        <v>-0.618</v>
       </c>
       <c r="E55" t="n">
         <v>-0.437</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2127</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.6194</v>
       </c>
       <c r="E56" t="n">
         <v>-0.4405</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2239</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6086</v>
+        <v>-0.6286</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4636</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2316</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6152</v>
+        <v>-0.635</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4797</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2965</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6694</v>
+        <v>-0.6885</v>
       </c>
       <c r="E59" t="n">
         <v>-0.614</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3087</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6796</v>
+        <v>-0.6986</v>
       </c>
       <c r="E60" t="n">
         <v>-0.6393</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3328</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6998</v>
+        <v>-0.7185</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6892</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3367</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.7217</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6973</v>
@@ -3308,7 +3308,7 @@
         <v>-0.3437</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7089</v>
+        <v>-0.7275</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7117</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3664</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7279</v>
+        <v>-0.7462</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7587</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5343</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.8847</v>
       </c>
       <c r="E65" t="n">
         <v>-1.1065</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5377</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8712</v>
+        <v>-0.8875</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1135</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5695</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8978</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1794</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5785</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9053</v>
+        <v>-0.9212</v>
       </c>
       <c r="E68" t="n">
         <v>-1.198</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5931999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9176</v>
+        <v>-0.9333</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2285</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5938</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9181</v>
+        <v>-0.9338</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2297</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.237</v>
+        <v>-1.2361</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.5969</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9211</v>
+        <v>-0.9364</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.237</v>
+        <v>-1.2361</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.237</v>
+        <v>-0.2361</v>
       </c>
       <c r="G71" t="n">
         <v>-1</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.237</v>
+        <v>-0.2361</v>
       </c>
       <c r="I71" t="n">
         <v>-0.2381</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6165</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9371</v>
+        <v>-0.9525</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2767</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6637</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9766</v>
+        <v>-0.9915</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3744</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7255</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0283</v>
+        <v>-1.0425</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5025</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7399</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0403</v>
+        <v>-1.0543</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5322</v>
@@ -3906,7 +3906,7 @@
         <v>-0.749</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.048</v>
+        <v>-1.0619</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5511</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7642</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0607</v>
+        <v>-1.0744</v>
       </c>
       <c r="E77" t="n">
         <v>-1.5826</v>
@@ -3998,7 +3998,7 @@
         <v>-0.7978</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0888</v>
+        <v>-1.1021</v>
       </c>
       <c r="E78" t="n">
         <v>-1.6521</v>
@@ -4044,7 +4044,7 @@
         <v>-0.9639</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2278</v>
+        <v>-1.2392</v>
       </c>
       <c r="E79" t="n">
         <v>-1.9962</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0988</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3406</v>
+        <v>-1.3505</v>
       </c>
       <c r="E80" t="n">
         <v>-2.2755</v>
@@ -4136,7 +4136,7 @@
         <v>-1.4006</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5931</v>
+        <v>-1.5995</v>
       </c>
       <c r="E81" t="n">
         <v>-2.9006</v>
